--- a/data/trans_camb/P2C_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,99</t>
+          <t>-0,59; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,0</t>
+          <t>-0,58; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 39,04</t>
+          <t>24,01; 38,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,94</t>
+          <t>-0,77; 0,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,79</t>
+          <t>-0,9; 0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,47; 36,99</t>
+          <t>28,34; 37,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,76</t>
+          <t>-0,47; 0,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,56</t>
+          <t>-0,63; 0,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,75; 36,18</t>
+          <t>28,41; 35,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-84,99; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2054,31; 24969,13</t>
+          <t>2653,0; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,73; 287,14</t>
+          <t>-73,38; 293,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,38; 307,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2102,67; 13959,98</t>
+          <t>1906,6; 10685,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 266,95</t>
+          <t>-53,65; 216,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 215,73</t>
+          <t>-73,33; 183,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2662,07; 11741,35</t>
+          <t>2563,38; 11179,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,25</t>
+          <t>-1,09; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,42</t>
+          <t>-0,28; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 14,84</t>
+          <t>7,6; 15,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,91</t>
+          <t>-0,57; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,58</t>
+          <t>-0,78; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,62</t>
+          <t>1,16; 7,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,47</t>
+          <t>-0,53; 0,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,78</t>
+          <t>-0,34; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,37</t>
+          <t>2,57; 9,38</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,9; 1389,77</t>
+          <t>-55,11; 1069,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534,71; 10701,32</t>
+          <t>650,3; 12867,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 388,35</t>
+          <t>-62,39; 360,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 337,96</t>
+          <t>-72,6; 309,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,26; 2114,1</t>
+          <t>106,86; 1993,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-57,53; 168,63</t>
+          <t>-63,48; 178,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 253,17</t>
+          <t>-43,22; 279,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>387,92; 2741,66</t>
+          <t>414,03; 2902,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,56</t>
+          <t>-0,04; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,88</t>
+          <t>-1,78; 1,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 26,64</t>
+          <t>5,17; 28,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,51</t>
+          <t>-0,28; 5,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,51</t>
+          <t>-0,46; 4,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,75</t>
+          <t>5,57; 15,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,73</t>
+          <t>0,5; 4,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,63</t>
+          <t>-0,52; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 19,06</t>
+          <t>7,08; 19,08</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 1447,03</t>
+          <t>-25,7; 1017,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177,55; 4968,19</t>
+          <t>156,16; 4492,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 1175,87</t>
+          <t>-39,48; 1188,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 887,98</t>
+          <t>-40,69; 956,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>165,88; 3386,32</t>
+          <t>153,32; 2783,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,31; 636,19</t>
+          <t>21,0; 791,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 356,78</t>
+          <t>-32,27; 378,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>355,73; 2284,36</t>
+          <t>324,32; 2349,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,74</t>
+          <t>-0,42; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,96</t>
+          <t>-0,25; 0,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,81; 19,58</t>
+          <t>13,09; 19,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,0</t>
+          <t>-0,2; 0,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,78</t>
+          <t>-0,38; 0,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 17,18</t>
+          <t>6,21; 17,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,7</t>
+          <t>-0,09; 0,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,67</t>
+          <t>-0,17; 0,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,93</t>
+          <t>8,04; 16,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 227,96</t>
+          <t>-48,99; 229,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 287,52</t>
+          <t>-33,93; 268,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1366,95; 5871,34</t>
+          <t>1408,03; 5702,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 199,71</t>
+          <t>-21,44; 185,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 153,3</t>
+          <t>-38,66; 149,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>719,46; 2913,77</t>
+          <t>660,56; 2836,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 147,22</t>
+          <t>-16,2; 138,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 131,56</t>
+          <t>-20,95; 135,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1087,53; 3176,01</t>
+          <t>1139,86; 3218,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>30,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,58</t>
+          <t>31,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>31,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,86</t>
+          <t>-0,57; 0,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,92</t>
+          <t>-0,59; 0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 38,63</t>
+          <t>23,64; 37,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,95</t>
+          <t>-0,71; 0,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,82</t>
+          <t>-0,94; 0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 37,55</t>
+          <t>27,33; 36,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,74</t>
+          <t>-0,45; 0,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,6</t>
+          <t>-0,63; 0,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,41; 35,8</t>
+          <t>27,6; 35,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7316,66%</t>
+          <t>7102,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4435,57%</t>
+          <t>4270,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5273,87%</t>
+          <t>5091,46%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-84,99; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2653,0; —</t>
+          <t>2480,8; 25985,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 293,86</t>
+          <t>-66,17; 335,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,38; 307,61</t>
+          <t>-84,81; 278,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1906,6; 10685,76</t>
+          <t>1969,42; 10549,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,65; 216,96</t>
+          <t>-55,31; 209,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 183,25</t>
+          <t>-66,13; 187,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2563,38; 11179,77</t>
+          <t>2709,72; 9967,21</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,98</t>
+          <t>9,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>8,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,25</t>
+          <t>-1,08; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,43</t>
+          <t>-0,29; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 15,21</t>
+          <t>6,89; 13,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,98</t>
+          <t>-0,58; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,62</t>
+          <t>-0,75; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,59</t>
+          <t>5,02; 9,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,48</t>
+          <t>-0,49; 0,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,77</t>
+          <t>-0,28; 0,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,38</t>
+          <t>6,5; 10,41</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2274,15%</t>
+          <t>1965,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>659,34%</t>
+          <t>1135,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1172,56%</t>
+          <t>1475,21%</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 1069,93</t>
+          <t>-50,99; 1084,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650,3; 12867,85</t>
+          <t>553,71; 9852,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 360,81</t>
+          <t>-64,37; 412,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 309,93</t>
+          <t>-76,09; 231,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>106,86; 1993,47</t>
+          <t>434,48; 3627,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 178,89</t>
+          <t>-60,75; 212,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 279,43</t>
+          <t>-37,63; 275,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>414,03; 2902,9</t>
+          <t>663,47; 3402,93</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,19</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,56</t>
+          <t>10,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,87</t>
+          <t>0,13; 6,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,95</t>
+          <t>-1,53; 1,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 28,51</t>
+          <t>4,95; 26,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,9</t>
+          <t>-0,33; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,61</t>
+          <t>-0,5; 4,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 15,98</t>
+          <t>4,88; 15,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,77</t>
+          <t>0,51; 4,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,69</t>
+          <t>-0,51; 2,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 19,08</t>
+          <t>5,83; 17,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1058,92%</t>
+          <t>976,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>704,03%</t>
+          <t>637,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>863,57%</t>
+          <t>788,37%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 1017,72</t>
+          <t>-31,4; 1157,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>156,16; 4492,68</t>
+          <t>145,71; 5083,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 1188,24</t>
+          <t>-37,68; 1145,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 956,42</t>
+          <t>-41,17; 835,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>153,32; 2783,18</t>
+          <t>164,73; 2992,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,0; 791,31</t>
+          <t>7,63; 603,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 378,45</t>
+          <t>-35,01; 351,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>324,32; 2349,33</t>
+          <t>262,71; 2097,54</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,07</t>
+          <t>14,57</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>15,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>15,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,73</t>
+          <t>-0,39; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,94</t>
+          <t>-0,28; 0,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,09; 19,55</t>
+          <t>11,86; 18,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,99</t>
+          <t>-0,25; 0,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,77</t>
+          <t>-0,36; 0,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 17,28</t>
+          <t>13,87; 18,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,69</t>
+          <t>-0,07; 0,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,68</t>
+          <t>-0,15; 0,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,84</t>
+          <t>13,68; 17,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2776,42%</t>
+          <t>2517,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1633,05%</t>
+          <t>2055,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2023,7%</t>
+          <t>2241,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 229,76</t>
+          <t>-46,6; 233,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 268,86</t>
+          <t>-40,59; 281,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1408,03; 5702,45</t>
+          <t>1162,87; 5462,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 185,34</t>
+          <t>-23,94; 188,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 149,64</t>
+          <t>-35,71; 154,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>660,56; 2836,0</t>
+          <t>1159,69; 3675,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 138,22</t>
+          <t>-11,61; 141,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 135,55</t>
+          <t>-17,98; 139,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1139,86; 3218,12</t>
+          <t>1434,5; 3506,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
